--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914055</v>
+        <v>124916072</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>57942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R2" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +787,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914053</v>
+        <v>124914051</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>57995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124916072</v>
+        <v>124914041</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,26 +962,30 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R4" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,22 +1039,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914051</v>
+        <v>124914046</v>
       </c>
       <c r="B5" t="n">
-        <v>57995</v>
+        <v>57847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,21 +1067,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1171,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914046</v>
+        <v>124914053</v>
       </c>
       <c r="B6" t="n">
-        <v>57847</v>
+        <v>58055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,20 +1187,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1206,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1295,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914041</v>
+        <v>124914055</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>58191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,20 +1311,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1334,14 +1338,10 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914051</v>
+        <v>124914041</v>
       </c>
       <c r="B3" t="n">
-        <v>57995</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,10 +838,14 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914041</v>
+        <v>124914051</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,14 +966,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914046</v>
+        <v>124914055</v>
       </c>
       <c r="B5" t="n">
-        <v>57847</v>
+        <v>58191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,20 +1063,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914053</v>
+        <v>124914046</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
+        <v>57847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,20 +1187,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914055</v>
+        <v>124914053</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,16 +1315,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124916072</v>
+        <v>124914055</v>
       </c>
       <c r="B2" t="n">
-        <v>57942</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R2" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +787,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914041</v>
+        <v>124914051</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,14 +838,10 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914051</v>
+        <v>124916072</v>
       </c>
       <c r="B4" t="n">
-        <v>57995</v>
+        <v>57942</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,17 +971,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R4" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,22 +1035,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914055</v>
+        <v>124914053</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,16 +1063,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,7 +1082,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1299,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914053</v>
+        <v>124914041</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,20 +1307,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1334,14 +1330,18 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914055</v>
+        <v>124914053</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124916072</v>
+        <v>124914055</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,25 +935,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -971,17 +971,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R4" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,22 +1035,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914053</v>
+        <v>124914041</v>
       </c>
       <c r="B5" t="n">
-        <v>58055</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,20 +1059,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,14 +1082,18 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1295,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914041</v>
+        <v>124916072</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57942</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,21 +1315,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,30 +1338,26 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R7" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,12 +1411,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914053</v>
+        <v>124914041</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +710,18 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914051</v>
+        <v>124916072</v>
       </c>
       <c r="B3" t="n">
-        <v>57995</v>
+        <v>57942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +819,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -847,17 +851,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R3" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914055</v>
+        <v>124914053</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +943,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,7 +962,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914041</v>
+        <v>124914046</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,16 +1067,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,14 +1090,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914046</v>
+        <v>124914051</v>
       </c>
       <c r="B6" t="n">
-        <v>57847</v>
+        <v>57995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124916072</v>
+        <v>124914055</v>
       </c>
       <c r="B7" t="n">
-        <v>57942</v>
+        <v>58191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,25 +1311,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1347,17 +1347,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R7" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,12 +1411,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914041</v>
+        <v>124916072</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,30 +714,26 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R2" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,22 +787,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124916072</v>
+        <v>124914046</v>
       </c>
       <c r="B3" t="n">
-        <v>57942</v>
+        <v>57847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -851,17 +847,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R3" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +911,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1051,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914046</v>
+        <v>124914055</v>
       </c>
       <c r="B5" t="n">
-        <v>57847</v>
+        <v>58191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,20 +1059,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1175,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914051</v>
+        <v>124914041</v>
       </c>
       <c r="B6" t="n">
-        <v>57995</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1187,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1214,10 +1210,14 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914055</v>
+        <v>124914051</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>57995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,25 +1311,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124916072</v>
+        <v>124914046</v>
       </c>
       <c r="B2" t="n">
-        <v>57942</v>
+        <v>57847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R2" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +787,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914046</v>
+        <v>124914053</v>
       </c>
       <c r="B3" t="n">
-        <v>57847</v>
+        <v>58055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914053</v>
+        <v>124914051</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>57995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914055</v>
+        <v>124914041</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,20 +1059,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,10 +1086,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1171,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914041</v>
+        <v>124914055</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>58191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,20 +1187,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,14 +1214,10 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914051</v>
+        <v>124916072</v>
       </c>
       <c r="B7" t="n">
-        <v>57995</v>
+        <v>57942</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1347,17 +1347,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R7" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,12 +1411,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914046</v>
+        <v>124914055</v>
       </c>
       <c r="B2" t="n">
-        <v>57847</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914053</v>
+        <v>124914041</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +834,18 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914041</v>
+        <v>124914046</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,16 +1067,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,14 +1090,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914055</v>
+        <v>124914053</v>
       </c>
       <c r="B6" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914055</v>
+        <v>124914051</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>57995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914041</v>
+        <v>124916072</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,30 +838,26 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R3" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914051</v>
+        <v>124914041</v>
       </c>
       <c r="B4" t="n">
-        <v>57995</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,10 +962,14 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124916072</v>
+        <v>124914055</v>
       </c>
       <c r="B7" t="n">
-        <v>57942</v>
+        <v>58191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,25 +1311,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1347,17 +1347,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R7" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,12 +1411,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914051</v>
+        <v>124914053</v>
       </c>
       <c r="B2" t="n">
-        <v>57995</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914041</v>
+        <v>124914046</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,14 +962,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1051,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914046</v>
+        <v>124914055</v>
       </c>
       <c r="B5" t="n">
-        <v>57847</v>
+        <v>58191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,20 +1059,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1175,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914053</v>
+        <v>124914051</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
+        <v>57995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,30 +1183,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1299,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914055</v>
+        <v>124914041</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,20 +1307,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1338,10 +1334,14 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914053</v>
+        <v>124914055</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>58305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124916072</v>
+        <v>124914046</v>
       </c>
       <c r="B3" t="n">
-        <v>57942</v>
+        <v>57961</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -847,17 +847,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R3" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914046</v>
+        <v>124914041</v>
       </c>
       <c r="B4" t="n">
-        <v>57847</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,10 +962,14 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914055</v>
+        <v>124916072</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>58060</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1063,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1095,17 +1099,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R5" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,22 +1163,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914051</v>
+        <v>124914053</v>
       </c>
       <c r="B6" t="n">
-        <v>57995</v>
+        <v>58167</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,30 +1187,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1295,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914041</v>
+        <v>124914051</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>58111</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,21 +1315,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,14 +1338,10 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914046</v>
+        <v>124914041</v>
       </c>
       <c r="B3" t="n">
-        <v>57961</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,10 +838,14 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914041</v>
+        <v>124914046</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>57961</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +943,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,14 +966,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124916072</v>
+        <v>124914051</v>
       </c>
       <c r="B5" t="n">
-        <v>58060</v>
+        <v>58111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,21 +1067,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1099,17 +1099,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R5" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,12 +1163,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124914051</v>
+        <v>124916072</v>
       </c>
       <c r="B7" t="n">
-        <v>58111</v>
+        <v>58060</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1347,17 +1347,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R7" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,12 +1411,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 13704-2024 artfynd.xlsx
+++ b/artfynd/A 13704-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124914055</v>
+        <v>124914051</v>
       </c>
       <c r="B2" t="n">
-        <v>58305</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -799,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124914041</v>
+        <v>124916072</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,30 +828,26 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linje 8, Vrm</t>
+          <t>Svenstorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394478</v>
+        <v>394499</v>
       </c>
       <c r="R3" t="n">
-        <v>6580932</v>
+        <v>6580802</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,44 +901,39 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Oscar Gustavsson</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124914046</v>
+        <v>124914055</v>
       </c>
       <c r="B4" t="n">
-        <v>57961</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1051,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124914051</v>
+        <v>124914041</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1090,10 +1066,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1175,32 +1155,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124914053</v>
+        <v>124914046</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57961</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1299,42 +1274,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124916072</v>
+        <v>124914053</v>
       </c>
       <c r="B7" t="n">
-        <v>58060</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1347,17 +1317,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svenstorp, Vrm</t>
+          <t>Linje 8, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394499</v>
+        <v>394478</v>
       </c>
       <c r="R7" t="n">
-        <v>6580802</v>
+        <v>6580932</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,12 +1381,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Oscar Gustavsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
